--- a/output/pdf_financials_xlsx/DSV.xlsx
+++ b/output/pdf_financials_xlsx/DSV.xlsx
@@ -1183,22 +1183,22 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>3.588611</v>
+        <v>-3.588611</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>7.030627</v>
+        <v>-7.030627</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>9.656554</v>
+        <v>-9.656554</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>35.466515</v>
+        <v>-35.466515</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>41.09577</v>
+        <v>-41.09577</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>15.752515</v>
+        <v>-15.752515</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>-15.167</v>
@@ -1439,22 +1439,22 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>3.588611</v>
+        <v>-3.588611</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>7.030627</v>
+        <v>-7.030627</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>9.656554</v>
+        <v>-9.656554</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>35.466515</v>
+        <v>-35.466515</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>41.09577</v>
+        <v>-41.09577</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>15.752515</v>
+        <v>-15.752515</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>-15.167</v>
@@ -1590,22 +1590,22 @@
         <v>4.689309</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>3.588611</v>
+        <v>-3.588611</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>7.030627</v>
+        <v>-7.030627</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>9.656554</v>
+        <v>-9.656554</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>35.466515</v>
+        <v>-35.466515</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>41.09577</v>
+        <v>-41.09577</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>15.752515</v>
+        <v>-15.752515</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>-15.167</v>
@@ -1766,19 +1766,19 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-70.30627</v>
+        <v>70.30627</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-120.706925</v>
+        <v>120.706925</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-322.422864</v>
+        <v>322.422864</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-342.46475</v>
+        <v>342.46475</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-393.812875</v>
+        <v>393.812875</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>303.34</v>
@@ -1816,22 +1816,22 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>3.588611</v>
+        <v>-3.588611</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>7.030627</v>
+        <v>-7.030627</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>9.656554</v>
+        <v>-9.656554</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>35.466515</v>
+        <v>-35.466515</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>41.09577</v>
+        <v>-41.09577</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>15.752515</v>
+        <v>-15.752515</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-15.167</v>
@@ -1918,22 +1918,22 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>3.588611</v>
+        <v>-3.588611</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>7.082158</v>
+        <v>-6.979096</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>9.774224999999999</v>
+        <v>-9.538883</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>35.65826</v>
+        <v>-35.27477</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>41.385108</v>
+        <v>-40.806432</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>16.116259</v>
+        <v>-15.388771</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-14.89</v>
@@ -2044,22 +2044,22 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>-0</v>
@@ -5747,22 +5747,22 @@
         <v>0</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0</v>
+        <v>0.000914</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0</v>
+        <v>-0.478451</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0</v>
+        <v>-0.121464</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>0</v>
+        <v>-0.039076</v>
       </c>
       <c r="M103" s="3" t="n">
-        <v>0</v>
+        <v>-0.032776</v>
       </c>
       <c r="N103" s="3" t="n">
-        <v>0</v>
+        <v>0.012574</v>
       </c>
       <c r="O103" s="3" t="n">
         <v>0</v>
@@ -5894,22 +5894,22 @@
         <v>0.644937</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>-0.983954</v>
+        <v>-0.98304</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>-0.612222</v>
+        <v>-1.090673</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>-2.958984</v>
+        <v>-3.080448</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>-4.599827</v>
+        <v>-4.638903</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>5.811062</v>
+        <v>5.778286</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>-6.874</v>
+        <v>-6.861426</v>
       </c>
       <c r="O106" s="3" t="n">
         <v>41.07</v>
@@ -10554,7 +10554,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -12048,7 +12052,11 @@
           <t>Prepaids and deposits 8</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -13308,7 +13316,11 @@
           <t>Prepaids and deposits 9</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -13738,7 +13750,11 @@
           <t>Prepaids and deposits 36,873</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -15132,7 +15148,11 @@
           <t>Prepaids and deposits 7 37,787</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -25206,7 +25226,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -26996,7 +27020,11 @@
           <t>Prepaids and deposits 8</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -29042,7 +29070,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -30426,7 +30458,11 @@
           <t>Prepaids and deposits 914</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -32250,7 +32286,11 @@
           <t>Prepaids and deposits 7 39,941</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -42193,16 +42233,16 @@
         </is>
       </c>
       <c r="N404" s="5" t="n">
-        <v>35.466515</v>
+        <v>-35.466515</v>
       </c>
       <c r="O404" s="5" t="n">
-        <v>41.09577</v>
+        <v>-41.09577</v>
       </c>
       <c r="P404" s="5" t="n">
-        <v>15.752515</v>
+        <v>-15.752515</v>
       </c>
       <c r="Q404" s="5" t="n">
-        <v>20.895391</v>
+        <v>-20.895391</v>
       </c>
       <c r="R404" t="inlineStr">
         <is>
@@ -44809,10 +44849,10 @@
         </is>
       </c>
       <c r="L435" s="5" t="n">
-        <v>7.030627</v>
+        <v>-7.030627</v>
       </c>
       <c r="M435" s="5" t="n">
-        <v>9.656554</v>
+        <v>-9.656554</v>
       </c>
       <c r="N435" t="inlineStr">
         <is>
@@ -44981,10 +45021,10 @@
         </is>
       </c>
       <c r="L437" s="5" t="n">
-        <v>6.787156</v>
+        <v>-6.787156</v>
       </c>
       <c r="M437" s="5" t="n">
-        <v>9.595837</v>
+        <v>-9.595837</v>
       </c>
       <c r="N437" t="inlineStr">
         <is>
@@ -45660,10 +45700,10 @@
         </is>
       </c>
       <c r="K445" s="5" t="n">
-        <v>3.588611</v>
+        <v>-3.588611</v>
       </c>
       <c r="L445" s="5" t="n">
-        <v>1.901029</v>
+        <v>-1.901029</v>
       </c>
       <c r="M445" t="inlineStr">
         <is>
@@ -46688,7 +46728,7 @@
         </is>
       </c>
       <c r="K457" s="5" t="n">
-        <v>3.588611</v>
+        <v>-3.588611</v>
       </c>
       <c r="L457" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/DSV.xlsx
+++ b/output/pdf_financials_xlsx/DSV.xlsx
@@ -982,22 +982,22 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.113826</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.123611</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.834904</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-1.243369</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-3.095468</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-2.201088</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>0</v>
@@ -1819,22 +1819,22 @@
         <v>-3.588611</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-7.030627</v>
+        <v>-6.916801</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-9.656554</v>
+        <v>-9.532943</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-35.466515</v>
+        <v>-34.631611</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-41.09577</v>
+        <v>-39.852401</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-15.752515</v>
+        <v>-12.657047</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-15.167</v>
+        <v>-12.965912</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>149.521</v>
@@ -1921,22 +1921,22 @@
         <v>-3.588611</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-6.979096</v>
+        <v>-6.86527</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-9.538883</v>
+        <v>-9.415272</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-35.27477</v>
+        <v>-34.439866</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-40.806432</v>
+        <v>-39.563063</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-15.388771</v>
+        <v>-12.293303</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-14.89</v>
+        <v>-12.688912</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>251.112</v>
@@ -2168,10 +2168,10 @@
         <v>0.0008809999999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.003608</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.000387</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>1.059933</v>
@@ -2270,10 +2270,10 @@
         <v>0.0008809999999999999</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.003608</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.000387</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>1.059933</v>
@@ -13404,7 +13404,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -18280,7 +18284,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -41506,7 +41510,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -41586,7 +41590,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -44202,7 +44206,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">

--- a/output/pdf_financials_xlsx/DSV.xlsx
+++ b/output/pdf_financials_xlsx/DSV.xlsx
@@ -847,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0</v>
+        <v>47.512</v>
       </c>
     </row>
     <row r="10">
@@ -898,7 +898,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0</v>
+        <v>47.512</v>
       </c>
     </row>
     <row r="11">
@@ -40136,7 +40136,11 @@
           <t>Other operating costs 22</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E380" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DSV.xlsx
+++ b/output/pdf_financials_xlsx/DSV.xlsx
@@ -3905,25 +3905,25 @@
         <v>0</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.001554</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.087617</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.183108</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.162119</v>
       </c>
       <c r="M67" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.216</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>55.023</v>
       </c>
     </row>
     <row r="68">
@@ -5566,7 +5566,7 @@
         <v>-15.752515</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>115.277</v>
+        <v>-15.167</v>
       </c>
       <c r="O99" s="3" t="n">
         <v>106.81</v>
@@ -6105,10 +6105,10 @@
         <v>0</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.198</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>24.382</v>
       </c>
     </row>
     <row r="111">
@@ -20422,7 +20422,11 @@
           <t>Net Income (loss) $</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -20594,7 +20598,11 @@
           <t>Accretion 14,17</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -24718,7 +24726,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
